--- a/a.输入/批量实验配置.xlsx
+++ b/a.输入/批量实验配置.xlsx
@@ -197,10 +197,10 @@
     <t>shareDecayMin</t>
   </si>
   <si>
-    <t>aggressive</t>
-  </si>
-  <si>
-    <t>conservative</t>
+    <t>mode1</t>
+  </si>
+  <si>
+    <t>mode2</t>
   </si>
   <si>
     <t>key</t>
@@ -1092,7 +1092,6 @@
     </font>
     <font>
       <sz val="10.8"/>
-      <color rgb="FF333333"/>
       <name val="var(--monospace)"/>
       <charset val="134"/>
     </font>
@@ -1104,6 +1103,7 @@
     </font>
     <font>
       <sz val="10.8"/>
+      <color rgb="FF333333"/>
       <name val="var(--monospace)"/>
       <charset val="134"/>
     </font>
@@ -3014,16 +3014,16 @@
         <v>54</v>
       </c>
       <c r="C3">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D3">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E3">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F3">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="G3">
         <v>1</v>
@@ -3040,22 +3040,22 @@
         <v>55</v>
       </c>
       <c r="C4">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D4">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E4">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="F4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G4">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H4">
-        <v>0.2</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/a.输入/批量实验配置.xlsx
+++ b/a.输入/批量实验配置.xlsx
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="375" uniqueCount="174">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="433" uniqueCount="192">
   <si>
     <t>group_id</t>
   </si>
@@ -56,313 +56,382 @@
     <t>enabled</t>
   </si>
   <si>
+    <t>methodCompare</t>
+  </si>
+  <si>
+    <t>US_Backbone</t>
+  </si>
+  <si>
+    <t>nodeFirst</t>
+  </si>
+  <si>
+    <t>default</t>
+  </si>
+  <si>
+    <t>shortestPathFirstWithLoadBalancing</t>
+  </si>
+  <si>
+    <t>RSA</t>
+  </si>
+  <si>
+    <t>RDA</t>
+  </si>
+  <si>
+    <t>topo_func</t>
+  </si>
+  <si>
+    <t>minm</t>
+  </si>
+  <si>
+    <t>maxm</t>
+  </si>
+  <si>
+    <t>minc</t>
+  </si>
+  <si>
+    <t>maxc</t>
+  </si>
+  <si>
+    <t>minb</t>
+  </si>
+  <si>
+    <t>maxb</t>
+  </si>
+  <si>
+    <t>Abilene</t>
+  </si>
+  <si>
+    <t>Cogentco</t>
+  </si>
+  <si>
+    <t>Chinanet</t>
+  </si>
+  <si>
+    <t>requests_num</t>
+  </si>
+  <si>
+    <t>destNode_count</t>
+  </si>
+  <si>
+    <t>vnftype_num</t>
+  </si>
+  <si>
+    <t>vnf_num</t>
+  </si>
+  <si>
+    <t>maxbw</t>
+  </si>
+  <si>
+    <t>minbw</t>
+  </si>
+  <si>
+    <t>maxnr</t>
+  </si>
+  <si>
+    <t>minnr</t>
+  </si>
+  <si>
+    <t>maxt</t>
+  </si>
+  <si>
+    <t>mint</t>
+  </si>
+  <si>
+    <t>display_name</t>
+  </si>
+  <si>
+    <t>deploy_func</t>
+  </si>
+  <si>
+    <t>requests_type</t>
+  </si>
+  <si>
+    <t>fixed_func</t>
+  </si>
+  <si>
+    <t>sorted_func</t>
+  </si>
+  <si>
+    <t>online_mode</t>
+  </si>
+  <si>
+    <t>RdaWeightTest1</t>
+  </si>
+  <si>
+    <t>RDA1</t>
+  </si>
+  <si>
+    <t>ResourceAndDelayAwareOnline</t>
+  </si>
+  <si>
+    <t>sortedRequests</t>
+  </si>
+  <si>
+    <t>FixedTreePlan</t>
+  </si>
+  <si>
+    <t>generateDeployPlan</t>
+  </si>
+  <si>
+    <t>RdaWeightTest2</t>
+  </si>
+  <si>
+    <t>RDA2</t>
+  </si>
+  <si>
+    <t>RdaWeightTest3</t>
+  </si>
+  <si>
+    <t>RDA3</t>
+  </si>
+  <si>
+    <t>RdaWeightTest4</t>
+  </si>
+  <si>
+    <t>RDA4</t>
+  </si>
+  <si>
+    <t>RdaWeightTest5</t>
+  </si>
+  <si>
+    <t>RDA5</t>
+  </si>
+  <si>
+    <t>RdaWeightTest6</t>
+  </si>
+  <si>
+    <t>RDA6</t>
+  </si>
+  <si>
+    <t>STB</t>
+  </si>
+  <si>
+    <t>NIF</t>
+  </si>
+  <si>
+    <t>requests</t>
+  </si>
+  <si>
+    <t>candLinkNum</t>
+  </si>
+  <si>
+    <t>candNodeNum</t>
+  </si>
+  <si>
+    <t>shareWeight</t>
+  </si>
+  <si>
+    <t>congWeight</t>
+  </si>
+  <si>
+    <t>delayWeight</t>
+  </si>
+  <si>
+    <t>shareDecayMin</t>
+  </si>
+  <si>
+    <t>weight1</t>
+  </si>
+  <si>
+    <t>weight2</t>
+  </si>
+  <si>
+    <t>weight3</t>
+  </si>
+  <si>
+    <t>weight4</t>
+  </si>
+  <si>
+    <t>weight5</t>
+  </si>
+  <si>
+    <t>weight6</t>
+  </si>
+  <si>
+    <t>说明</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t>RdaWeightTest1-6</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>：测试共享权重，拥塞权重，时延权重的比例</t>
+    </r>
+  </si>
+  <si>
+    <t>key</t>
+  </si>
+  <si>
+    <t>value</t>
+  </si>
+  <si>
+    <t>description</t>
+  </si>
+  <si>
+    <t>rng_seed_base</t>
+  </si>
+  <si>
+    <t>42</t>
+  </si>
+  <si>
+    <t>随机种子基数，保证实验可重复</t>
+  </si>
+  <si>
+    <t>output_dir</t>
+  </si>
+  <si>
+    <t>c.输出</t>
+  </si>
+  <si>
+    <t>输出根目录</t>
+  </si>
+  <si>
+    <t>summary_xlsx</t>
+  </si>
+  <si>
+    <t>实验结果汇总.xlsx</t>
+  </si>
+  <si>
+    <t>结果汇总文件名（在 output_dir 下）</t>
+  </si>
+  <si>
+    <t>plot_data_xlsx</t>
+  </si>
+  <si>
+    <t>绘图数据.xlsx</t>
+  </si>
+  <si>
+    <t>绘图数据文件名（在 output_dir 下）</t>
+  </si>
+  <si>
+    <t>fig_visible</t>
+  </si>
+  <si>
+    <t>off</t>
+  </si>
+  <si>
+    <t>绘图时是否显示窗口 (on/off)</t>
+  </si>
+  <si>
+    <t>save_svg</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>是否保存 SVG 图表 (1=是, 0=否)</t>
+  </si>
+  <si>
+    <t>save_mat</t>
+  </si>
+  <si>
+    <t>0</t>
+  </si>
+  <si>
+    <t>是否保存 MAT 结果文件 (1=是, 0=否)</t>
+  </si>
+  <si>
+    <t>svg_background</t>
+  </si>
+  <si>
+    <t>none</t>
+  </si>
+  <si>
+    <t>SVG 背景色 (none=透明)</t>
+  </si>
+  <si>
+    <t>fig_width</t>
+  </si>
+  <si>
+    <t>800</t>
+  </si>
+  <si>
+    <t>默认图宽（像素）</t>
+  </si>
+  <si>
+    <t>fig_height</t>
+  </si>
+  <si>
+    <t>600</t>
+  </si>
+  <si>
+    <t>默认图高（像素）</t>
+  </si>
+  <si>
+    <t>line_width</t>
+  </si>
+  <si>
+    <t>1.8</t>
+  </si>
+  <si>
+    <t>曲线线宽</t>
+  </si>
+  <si>
+    <t>font_size</t>
+  </si>
+  <si>
+    <t>12</t>
+  </si>
+  <si>
+    <t>图表字号</t>
+  </si>
+  <si>
+    <t>slack_mode</t>
+  </si>
+  <si>
+    <t>ratio</t>
+  </si>
+  <si>
+    <t>裕量模式 (ratio=比例, abs=绝对值)</t>
+  </si>
+  <si>
+    <t>e2e_source</t>
+  </si>
+  <si>
+    <t>auto</t>
+  </si>
+  <si>
+    <t>端到端时延来源 (auto=自动选择)</t>
+  </si>
+  <si>
+    <t>sheet1</t>
+  </si>
+  <si>
+    <t>定义要运行哪些实验组合。每行代表一组实验。</t>
+  </si>
+  <si>
+    <t>Sheet 5：方法参数组</t>
+  </si>
+  <si>
+    <t>字段</t>
+  </si>
+  <si>
+    <t>类型</t>
+  </si>
+  <si>
+    <t>示例</t>
+  </si>
+  <si>
+    <t>为特定方法定义参数变体，用于参数调优对比实验。</t>
+  </si>
+  <si>
+    <t>string</t>
+  </si>
+  <si>
+    <t>实验组标识，用于分组管理</t>
+  </si>
+  <si>
     <t>G1</t>
-  </si>
-  <si>
-    <t>US_Backbone</t>
-  </si>
-  <si>
-    <t>ResourceAndDelayAwareOnline</t>
-  </si>
-  <si>
-    <t>default</t>
-  </si>
-  <si>
-    <t>nodeFirst</t>
-  </si>
-  <si>
-    <t>1</t>
-  </si>
-  <si>
-    <t>shortestPathFirstWithLoadBalancing</t>
-  </si>
-  <si>
-    <t>RSA</t>
-  </si>
-  <si>
-    <t>topo_func</t>
-  </si>
-  <si>
-    <t>minm</t>
-  </si>
-  <si>
-    <t>maxm</t>
-  </si>
-  <si>
-    <t>minc</t>
-  </si>
-  <si>
-    <t>maxc</t>
-  </si>
-  <si>
-    <t>minb</t>
-  </si>
-  <si>
-    <t>maxb</t>
-  </si>
-  <si>
-    <t>Abilene</t>
-  </si>
-  <si>
-    <t>Cogentco</t>
-  </si>
-  <si>
-    <t>Chinanet</t>
-  </si>
-  <si>
-    <t>requests_num</t>
-  </si>
-  <si>
-    <t>destNode_count</t>
-  </si>
-  <si>
-    <t>vnftype_num</t>
-  </si>
-  <si>
-    <t>vnf_num</t>
-  </si>
-  <si>
-    <t>maxbw</t>
-  </si>
-  <si>
-    <t>minbw</t>
-  </si>
-  <si>
-    <t>maxnr</t>
-  </si>
-  <si>
-    <t>minnr</t>
-  </si>
-  <si>
-    <t>maxt</t>
-  </si>
-  <si>
-    <t>mint</t>
-  </si>
-  <si>
-    <t>display_name</t>
-  </si>
-  <si>
-    <t>deploy_func</t>
-  </si>
-  <si>
-    <t>requests_type</t>
-  </si>
-  <si>
-    <t>fixed_func</t>
-  </si>
-  <si>
-    <t>sorted_func</t>
-  </si>
-  <si>
-    <t>online_mode</t>
-  </si>
-  <si>
-    <t>STB</t>
-  </si>
-  <si>
-    <t>sortedRequests</t>
-  </si>
-  <si>
-    <t>FixedTreePlan</t>
-  </si>
-  <si>
-    <t>generateDeployPlan</t>
-  </si>
-  <si>
-    <t>NIF</t>
-  </si>
-  <si>
-    <t>requests</t>
-  </si>
-  <si>
-    <t>RDA</t>
-  </si>
-  <si>
-    <t>candLinkNum</t>
-  </si>
-  <si>
-    <t>candNodeNum</t>
-  </si>
-  <si>
-    <t>shareWeight</t>
-  </si>
-  <si>
-    <t>congWeight</t>
-  </si>
-  <si>
-    <t>delayWeight</t>
-  </si>
-  <si>
-    <t>shareDecayMin</t>
-  </si>
-  <si>
-    <t>mode1</t>
-  </si>
-  <si>
-    <t>mode2</t>
-  </si>
-  <si>
-    <t>key</t>
-  </si>
-  <si>
-    <t>value</t>
-  </si>
-  <si>
-    <t>description</t>
-  </si>
-  <si>
-    <t>rng_seed_base</t>
-  </si>
-  <si>
-    <t>42</t>
-  </si>
-  <si>
-    <t>随机种子基数，保证实验可重复</t>
-  </si>
-  <si>
-    <t>output_dir</t>
-  </si>
-  <si>
-    <t>c.输出</t>
-  </si>
-  <si>
-    <t>输出根目录</t>
-  </si>
-  <si>
-    <t>summary_xlsx</t>
-  </si>
-  <si>
-    <t>实验结果汇总.xlsx</t>
-  </si>
-  <si>
-    <t>结果汇总文件名（在 output_dir 下）</t>
-  </si>
-  <si>
-    <t>plot_data_xlsx</t>
-  </si>
-  <si>
-    <t>绘图数据.xlsx</t>
-  </si>
-  <si>
-    <t>绘图数据文件名（在 output_dir 下）</t>
-  </si>
-  <si>
-    <t>fig_visible</t>
-  </si>
-  <si>
-    <t>off</t>
-  </si>
-  <si>
-    <t>绘图时是否显示窗口 (on/off)</t>
-  </si>
-  <si>
-    <t>save_svg</t>
-  </si>
-  <si>
-    <t>是否保存 SVG 图表 (1=是, 0=否)</t>
-  </si>
-  <si>
-    <t>save_mat</t>
-  </si>
-  <si>
-    <t>0</t>
-  </si>
-  <si>
-    <t>是否保存 MAT 结果文件 (1=是, 0=否)</t>
-  </si>
-  <si>
-    <t>svg_background</t>
-  </si>
-  <si>
-    <t>none</t>
-  </si>
-  <si>
-    <t>SVG 背景色 (none=透明)</t>
-  </si>
-  <si>
-    <t>fig_width</t>
-  </si>
-  <si>
-    <t>800</t>
-  </si>
-  <si>
-    <t>默认图宽（像素）</t>
-  </si>
-  <si>
-    <t>fig_height</t>
-  </si>
-  <si>
-    <t>600</t>
-  </si>
-  <si>
-    <t>默认图高（像素）</t>
-  </si>
-  <si>
-    <t>line_width</t>
-  </si>
-  <si>
-    <t>1.8</t>
-  </si>
-  <si>
-    <t>曲线线宽</t>
-  </si>
-  <si>
-    <t>font_size</t>
-  </si>
-  <si>
-    <t>12</t>
-  </si>
-  <si>
-    <t>图表字号</t>
-  </si>
-  <si>
-    <t>slack_mode</t>
-  </si>
-  <si>
-    <t>ratio</t>
-  </si>
-  <si>
-    <t>裕量模式 (ratio=比例, abs=绝对值)</t>
-  </si>
-  <si>
-    <t>e2e_source</t>
-  </si>
-  <si>
-    <t>auto</t>
-  </si>
-  <si>
-    <t>端到端时延来源 (auto=自动选择)</t>
-  </si>
-  <si>
-    <t>sheet1</t>
-  </si>
-  <si>
-    <t>定义要运行哪些实验组合。每行代表一组实验。</t>
-  </si>
-  <si>
-    <t>Sheet 5：方法参数组</t>
-  </si>
-  <si>
-    <t>字段</t>
-  </si>
-  <si>
-    <t>类型</t>
-  </si>
-  <si>
-    <t>说明</t>
-  </si>
-  <si>
-    <t>示例</t>
-  </si>
-  <si>
-    <t>为特定方法定义参数变体，用于参数调优对比实验。</t>
-  </si>
-  <si>
-    <t>string</t>
-  </si>
-  <si>
-    <t>实验组标识，用于分组管理</t>
   </si>
   <si>
     <t>拓扑名称，对应"拓扑配置"sheet 中的行</t>
@@ -922,7 +991,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="26">
+  <fonts count="27">
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
@@ -937,6 +1006,11 @@
       <sz val="12"/>
       <color rgb="FF333333"/>
       <name val="仿宋"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
@@ -1091,11 +1165,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="10.8"/>
-      <name val="var(--monospace)"/>
-      <charset val="134"/>
-    </font>
-    <font>
       <sz val="12"/>
       <color rgb="FF333333"/>
       <name val="Helvetica"/>
@@ -1104,6 +1173,11 @@
     <font>
       <sz val="10.8"/>
       <color rgb="FF333333"/>
+      <name val="var(--monospace)"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="10.8"/>
       <name val="var(--monospace)"/>
       <charset val="134"/>
     </font>
@@ -1438,152 +1512,152 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="7" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1601,6 +1675,18 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -2135,8 +2221,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G13"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" outlineLevelCol="6"/>
+  <dimension ref="A1:I7"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" outlineLevelRow="6"/>
   <cols>
     <col min="1" max="2" width="16.2857142857143" customWidth="1"/>
     <col min="3" max="3" width="36.7142857142857" customWidth="1"/>
@@ -2146,7 +2232,7 @@
     <col min="7" max="7" width="13.7142857142857" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7">
+    <row r="1" spans="1:9">
       <c r="A1" s="7" t="s">
         <v>0</v>
       </c>
@@ -2169,17 +2255,17 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7">
+    <row r="2" spans="1:9">
       <c r="A2" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="B2" s="7" t="s">
+      <c r="B2" t="s">
         <v>8</v>
       </c>
-      <c r="C2" s="7" t="s">
+      <c r="C2" t="s">
         <v>9</v>
       </c>
-      <c r="D2" s="7" t="s">
+      <c r="D2" t="s">
         <v>10</v>
       </c>
       <c r="E2" s="7">
@@ -2191,22 +2277,23 @@
       <c r="G2" s="7">
         <v>1</v>
       </c>
-    </row>
-    <row r="3" spans="1:7">
+      <c r="I2" s="11"/>
+    </row>
+    <row r="3" spans="1:9">
       <c r="A3" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="B3" s="7" t="s">
+      <c r="B3" t="s">
         <v>8</v>
       </c>
-      <c r="C3" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="D3" s="7" t="s">
+      <c r="C3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D3" t="s">
         <v>10</v>
       </c>
       <c r="E3" s="7">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F3" s="7">
         <v>1</v>
@@ -2214,22 +2301,23 @@
       <c r="G3" s="7">
         <v>1</v>
       </c>
-    </row>
-    <row r="4" spans="1:7">
+      <c r="I3" s="11"/>
+    </row>
+    <row r="4" spans="1:9">
       <c r="A4" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="B4" s="7" t="s">
+      <c r="B4" t="s">
         <v>8</v>
       </c>
-      <c r="C4" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="D4" s="7" t="s">
+      <c r="C4" t="s">
+        <v>12</v>
+      </c>
+      <c r="D4" t="s">
         <v>10</v>
       </c>
       <c r="E4" s="7">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F4" s="7">
         <v>1</v>
@@ -2237,22 +2325,23 @@
       <c r="G4" s="7">
         <v>1</v>
       </c>
-    </row>
-    <row r="5" spans="1:7">
+      <c r="I4" s="11"/>
+    </row>
+    <row r="5" spans="1:9">
       <c r="A5" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="B5" s="7" t="s">
+      <c r="B5" t="s">
         <v>8</v>
       </c>
-      <c r="C5" s="7" t="s">
-        <v>11</v>
+      <c r="C5" t="s">
+        <v>13</v>
       </c>
       <c r="D5" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="E5" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="E5" s="7">
+        <v>1</v>
       </c>
       <c r="F5" s="7">
         <v>1</v>
@@ -2260,190 +2349,15 @@
       <c r="G5" s="7">
         <v>1</v>
       </c>
-    </row>
-    <row r="6" spans="1:7">
-      <c r="A6" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="B6" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="C6" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="D6" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="E6" s="7">
-        <v>2</v>
-      </c>
-      <c r="F6" s="7">
-        <v>1</v>
-      </c>
-      <c r="G6" s="7">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7">
-      <c r="A7" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="B7" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="C7" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="D7" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="E7" s="7">
-        <v>3</v>
-      </c>
-      <c r="F7" s="7">
-        <v>1</v>
-      </c>
-      <c r="G7" s="7">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7">
-      <c r="A8" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="B8" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="C8" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="D8" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="E8" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F8" s="7">
-        <v>1</v>
-      </c>
-      <c r="G8" s="7">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7">
-      <c r="A9" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="B9" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="C9" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="D9" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="E9" s="7">
-        <v>2</v>
-      </c>
-      <c r="F9" s="7">
-        <v>1</v>
-      </c>
-      <c r="G9" s="7">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7">
-      <c r="A10" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="B10" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="C10" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="D10" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="E10" s="7">
-        <v>3</v>
-      </c>
-      <c r="F10" s="7">
-        <v>1</v>
-      </c>
-      <c r="G10" s="7">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7">
-      <c r="A11" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="B11" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="C11" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="D11" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="E11" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F11" s="7">
-        <v>1</v>
-      </c>
-      <c r="G11" s="7">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7">
-      <c r="A12" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="B12" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="C12" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="D12" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="E12" s="7">
-        <v>2</v>
-      </c>
-      <c r="F12" s="7">
-        <v>1</v>
-      </c>
-      <c r="G12" s="7">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7">
-      <c r="A13" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="B13" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="C13" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="D13" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="E13" s="7">
-        <v>3</v>
-      </c>
-      <c r="F13" s="7">
-        <v>1</v>
-      </c>
-      <c r="G13" s="7">
-        <v>1</v>
-      </c>
+      <c r="I5" s="11"/>
+    </row>
+    <row r="7" spans="1:9">
+      <c r="A7" s="7"/>
+      <c r="B7" s="7"/>
+      <c r="D7" s="7"/>
+      <c r="E7" s="7"/>
+      <c r="F7" s="7"/>
+      <c r="G7" s="7"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2471,25 +2385,25 @@
         <v>1</v>
       </c>
       <c r="B1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C1" t="s">
         <v>15</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
         <v>16</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>17</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>18</v>
       </c>
-      <c r="F1" t="s">
+      <c r="G1" t="s">
         <v>19</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
         <v>20</v>
-      </c>
-      <c r="H1" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="2" spans="1:8">
@@ -2506,7 +2420,7 @@
         <v>120</v>
       </c>
       <c r="E2">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="F2">
         <v>120</v>
@@ -2520,10 +2434,10 @@
     </row>
     <row r="3" spans="1:8">
       <c r="A3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C3">
         <v>40</v>
@@ -2546,10 +2460,10 @@
     </row>
     <row r="4" spans="1:8">
       <c r="A4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C4">
         <v>60</v>
@@ -2572,10 +2486,10 @@
     </row>
     <row r="5" spans="1:8">
       <c r="A5" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B5" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C5">
         <v>50</v>
@@ -2626,34 +2540,34 @@
         <v>1</v>
       </c>
       <c r="B1" t="s">
+        <v>24</v>
+      </c>
+      <c r="C1" t="s">
         <v>25</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
         <v>26</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>27</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>28</v>
       </c>
-      <c r="F1" t="s">
+      <c r="G1" t="s">
         <v>29</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
         <v>30</v>
       </c>
-      <c r="H1" t="s">
+      <c r="I1" t="s">
         <v>31</v>
       </c>
-      <c r="I1" t="s">
+      <c r="J1" t="s">
         <v>32</v>
       </c>
-      <c r="J1" t="s">
+      <c r="K1" t="s">
         <v>33</v>
-      </c>
-      <c r="K1" t="s">
-        <v>34</v>
       </c>
     </row>
     <row r="2" spans="1:11">
@@ -2693,7 +2607,7 @@
     </row>
     <row r="3" spans="1:11">
       <c r="A3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B3">
         <v>100</v>
@@ -2728,7 +2642,7 @@
     </row>
     <row r="4" spans="1:11">
       <c r="A4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B4">
         <v>100</v>
@@ -2763,7 +2677,7 @@
     </row>
     <row r="5" spans="1:11">
       <c r="A5" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B5">
         <v>100</v>
@@ -2805,8 +2719,8 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G5"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" outlineLevelRow="4" outlineLevelCol="6"/>
+  <dimension ref="A1:G12"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" outlineLevelCol="6"/>
   <cols>
     <col min="1" max="1" width="33.1428571428571" customWidth="1"/>
     <col min="2" max="2" width="13.4285714285714" customWidth="1"/>
@@ -2822,113 +2736,251 @@
         <v>2</v>
       </c>
       <c r="B1" t="s">
+        <v>34</v>
+      </c>
+      <c r="C1" t="s">
         <v>35</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
         <v>36</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>37</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>38</v>
       </c>
-      <c r="F1" t="s">
+      <c r="G1" t="s">
         <v>39</v>
-      </c>
-      <c r="G1" t="s">
-        <v>40</v>
       </c>
     </row>
     <row r="2" spans="1:7">
       <c r="A2" t="s">
-        <v>13</v>
+        <v>40</v>
       </c>
       <c r="B2" t="s">
         <v>41</v>
       </c>
       <c r="C2" t="s">
-        <v>13</v>
+        <v>42</v>
       </c>
       <c r="D2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:7">
       <c r="A3" t="s">
-        <v>11</v>
+        <v>46</v>
       </c>
       <c r="B3" t="s">
+        <v>47</v>
+      </c>
+      <c r="C3" t="s">
+        <v>42</v>
+      </c>
+      <c r="D3" t="s">
+        <v>43</v>
+      </c>
+      <c r="E3" t="s">
+        <v>44</v>
+      </c>
+      <c r="F3" t="s">
         <v>45</v>
       </c>
-      <c r="C3" t="s">
-        <v>11</v>
-      </c>
-      <c r="D3" t="s">
-        <v>46</v>
-      </c>
-      <c r="E3" t="s">
-        <v>43</v>
-      </c>
-      <c r="F3" t="s">
-        <v>44</v>
-      </c>
       <c r="G3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:7">
       <c r="A4" t="s">
-        <v>14</v>
+        <v>48</v>
       </c>
       <c r="B4" t="s">
-        <v>14</v>
+        <v>49</v>
       </c>
       <c r="C4" t="s">
-        <v>14</v>
+        <v>42</v>
       </c>
       <c r="D4" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E4" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F4" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="G4">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:7">
       <c r="A5" t="s">
+        <v>50</v>
+      </c>
+      <c r="B5" t="s">
+        <v>51</v>
+      </c>
+      <c r="C5" t="s">
+        <v>42</v>
+      </c>
+      <c r="D5" t="s">
+        <v>43</v>
+      </c>
+      <c r="E5" t="s">
+        <v>44</v>
+      </c>
+      <c r="F5" t="s">
+        <v>45</v>
+      </c>
+      <c r="G5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7">
+      <c r="A6" t="s">
+        <v>52</v>
+      </c>
+      <c r="B6" t="s">
+        <v>53</v>
+      </c>
+      <c r="C6" t="s">
+        <v>42</v>
+      </c>
+      <c r="D6" t="s">
+        <v>43</v>
+      </c>
+      <c r="E6" t="s">
+        <v>44</v>
+      </c>
+      <c r="F6" t="s">
+        <v>45</v>
+      </c>
+      <c r="G6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7">
+      <c r="A7" t="s">
+        <v>54</v>
+      </c>
+      <c r="B7" t="s">
+        <v>55</v>
+      </c>
+      <c r="C7" t="s">
+        <v>42</v>
+      </c>
+      <c r="D7" t="s">
+        <v>43</v>
+      </c>
+      <c r="E7" t="s">
+        <v>44</v>
+      </c>
+      <c r="F7" t="s">
+        <v>45</v>
+      </c>
+      <c r="G7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7">
+      <c r="A9" t="s">
+        <v>11</v>
+      </c>
+      <c r="B9" t="s">
+        <v>56</v>
+      </c>
+      <c r="C9" t="s">
+        <v>11</v>
+      </c>
+      <c r="D9" t="s">
+        <v>43</v>
+      </c>
+      <c r="E9" t="s">
+        <v>44</v>
+      </c>
+      <c r="F9" t="s">
+        <v>45</v>
+      </c>
+      <c r="G9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7">
+      <c r="A10" t="s">
         <v>9</v>
       </c>
-      <c r="B5" t="s">
-        <v>47</v>
-      </c>
-      <c r="C5" t="s">
+      <c r="B10" t="s">
+        <v>57</v>
+      </c>
+      <c r="C10" t="s">
         <v>9</v>
       </c>
-      <c r="D5" t="s">
+      <c r="D10" t="s">
+        <v>58</v>
+      </c>
+      <c r="E10" t="s">
+        <v>44</v>
+      </c>
+      <c r="F10" t="s">
+        <v>45</v>
+      </c>
+      <c r="G10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7">
+      <c r="A11" t="s">
+        <v>12</v>
+      </c>
+      <c r="B11" t="s">
+        <v>12</v>
+      </c>
+      <c r="C11" t="s">
+        <v>12</v>
+      </c>
+      <c r="D11" t="s">
+        <v>43</v>
+      </c>
+      <c r="E11" t="s">
+        <v>44</v>
+      </c>
+      <c r="F11" t="s">
+        <v>45</v>
+      </c>
+      <c r="G11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7">
+      <c r="A12" t="s">
+        <v>13</v>
+      </c>
+      <c r="B12" t="s">
+        <v>13</v>
+      </c>
+      <c r="C12" t="s">
         <v>42</v>
       </c>
-      <c r="E5" t="s">
+      <c r="D12" t="s">
         <v>43</v>
       </c>
-      <c r="F5" t="s">
+      <c r="E12" t="s">
         <v>44</v>
       </c>
-      <c r="G5">
+      <c r="F12" t="s">
+        <v>45</v>
+      </c>
+      <c r="G12">
         <v>1</v>
       </c>
     </row>
@@ -2941,8 +2993,8 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:H4"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" outlineLevelRow="3" outlineLevelCol="7"/>
+  <dimension ref="A1:R10"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="33.1428571428571" customWidth="1"/>
     <col min="2" max="2" width="12.8571428571429" customWidth="1"/>
@@ -2954,7 +3006,7 @@
     <col min="8" max="8" width="14.7142857142857" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8">
+    <row r="1" spans="1:18">
       <c r="A1" t="s">
         <v>2</v>
       </c>
@@ -2962,30 +3014,30 @@
         <v>3</v>
       </c>
       <c r="C1" t="s">
-        <v>48</v>
+        <v>59</v>
       </c>
       <c r="D1" t="s">
-        <v>49</v>
+        <v>60</v>
       </c>
       <c r="E1" t="s">
-        <v>50</v>
+        <v>61</v>
       </c>
       <c r="F1" t="s">
-        <v>51</v>
+        <v>62</v>
       </c>
       <c r="G1" t="s">
-        <v>52</v>
+        <v>63</v>
       </c>
       <c r="H1" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="2" spans="1:18">
       <c r="A2" t="s">
-        <v>9</v>
+        <v>40</v>
       </c>
       <c r="B2" t="s">
-        <v>10</v>
+        <v>65</v>
       </c>
       <c r="C2">
         <v>5</v>
@@ -3000,18 +3052,18 @@
         <v>1</v>
       </c>
       <c r="G2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H2">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:8">
+    <row r="3" spans="1:18">
       <c r="A3" t="s">
-        <v>9</v>
+        <v>46</v>
       </c>
       <c r="B3" t="s">
-        <v>54</v>
+        <v>66</v>
       </c>
       <c r="C3">
         <v>5</v>
@@ -3020,7 +3072,7 @@
         <v>5</v>
       </c>
       <c r="E3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F3">
         <v>1</v>
@@ -3032,12 +3084,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:8">
+    <row r="4" spans="1:18">
       <c r="A4" t="s">
-        <v>9</v>
+        <v>48</v>
       </c>
       <c r="B4" t="s">
-        <v>55</v>
+        <v>67</v>
       </c>
       <c r="C4">
         <v>5</v>
@@ -3046,10 +3098,10 @@
         <v>5</v>
       </c>
       <c r="E4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G4">
         <v>1</v>
@@ -3058,7 +3110,155 @@
         <v>0</v>
       </c>
     </row>
+    <row r="5" spans="1:18">
+      <c r="A5" t="s">
+        <v>50</v>
+      </c>
+      <c r="B5" t="s">
+        <v>68</v>
+      </c>
+      <c r="C5">
+        <v>5</v>
+      </c>
+      <c r="D5">
+        <v>5</v>
+      </c>
+      <c r="E5">
+        <v>1</v>
+      </c>
+      <c r="F5">
+        <v>1</v>
+      </c>
+      <c r="G5">
+        <v>2</v>
+      </c>
+      <c r="H5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:18">
+      <c r="A6" t="s">
+        <v>52</v>
+      </c>
+      <c r="B6" t="s">
+        <v>69</v>
+      </c>
+      <c r="C6">
+        <v>5</v>
+      </c>
+      <c r="D6">
+        <v>5</v>
+      </c>
+      <c r="E6">
+        <v>1</v>
+      </c>
+      <c r="F6">
+        <v>1</v>
+      </c>
+      <c r="G6">
+        <v>3</v>
+      </c>
+      <c r="H6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:18">
+      <c r="A7" t="s">
+        <v>54</v>
+      </c>
+      <c r="B7" t="s">
+        <v>70</v>
+      </c>
+      <c r="C7">
+        <v>5</v>
+      </c>
+      <c r="D7">
+        <v>5</v>
+      </c>
+      <c r="E7">
+        <v>1</v>
+      </c>
+      <c r="F7">
+        <v>1</v>
+      </c>
+      <c r="G7">
+        <v>4</v>
+      </c>
+      <c r="H7">
+        <v>0</v>
+      </c>
+      <c r="K7" s="8" t="s">
+        <v>71</v>
+      </c>
+      <c r="L7" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="M7" s="10"/>
+      <c r="N7" s="10"/>
+      <c r="O7" s="10"/>
+      <c r="P7" s="10"/>
+      <c r="Q7" s="10"/>
+      <c r="R7" s="10"/>
+    </row>
+    <row r="8" spans="1:18">
+      <c r="K8" s="10"/>
+      <c r="L8" s="10"/>
+      <c r="M8" s="10"/>
+      <c r="N8" s="10"/>
+      <c r="O8" s="10"/>
+      <c r="P8" s="10"/>
+      <c r="Q8" s="10"/>
+      <c r="R8" s="10"/>
+    </row>
+    <row r="9" spans="1:18">
+      <c r="A9" t="s">
+        <v>13</v>
+      </c>
+      <c r="B9" t="s">
+        <v>13</v>
+      </c>
+      <c r="C9">
+        <v>5</v>
+      </c>
+      <c r="D9">
+        <v>5</v>
+      </c>
+      <c r="E9">
+        <v>1</v>
+      </c>
+      <c r="F9">
+        <v>1</v>
+      </c>
+      <c r="G9">
+        <v>2</v>
+      </c>
+      <c r="H9">
+        <v>0</v>
+      </c>
+      <c r="K9" s="10"/>
+      <c r="L9" s="10"/>
+      <c r="M9" s="10"/>
+      <c r="N9" s="10"/>
+      <c r="O9" s="10"/>
+      <c r="P9" s="10"/>
+      <c r="Q9" s="10"/>
+      <c r="R9" s="10"/>
+    </row>
+    <row r="10" spans="1:18">
+      <c r="K10" s="10"/>
+      <c r="L10" s="10"/>
+      <c r="M10" s="10"/>
+      <c r="N10" s="10"/>
+      <c r="O10" s="10"/>
+      <c r="P10" s="10"/>
+      <c r="Q10" s="10"/>
+      <c r="R10" s="10"/>
+    </row>
   </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="K7:K10"/>
+    <mergeCell ref="L7:R10"/>
+  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
 </worksheet>
@@ -3077,167 +3277,167 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" t="s">
-        <v>56</v>
+        <v>73</v>
       </c>
       <c r="B1" t="s">
-        <v>57</v>
+        <v>74</v>
       </c>
       <c r="C1" t="s">
-        <v>58</v>
+        <v>75</v>
       </c>
     </row>
     <row r="2" spans="1:3">
       <c r="A2" t="s">
-        <v>59</v>
+        <v>76</v>
       </c>
       <c r="B2" t="s">
-        <v>60</v>
+        <v>77</v>
       </c>
       <c r="C2" t="s">
-        <v>61</v>
+        <v>78</v>
       </c>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" t="s">
-        <v>62</v>
+        <v>79</v>
       </c>
       <c r="B3" t="s">
-        <v>63</v>
+        <v>80</v>
       </c>
       <c r="C3" t="s">
-        <v>64</v>
+        <v>81</v>
       </c>
     </row>
     <row r="4" spans="1:3">
       <c r="A4" t="s">
-        <v>65</v>
+        <v>82</v>
       </c>
       <c r="B4" t="s">
-        <v>66</v>
+        <v>83</v>
       </c>
       <c r="C4" t="s">
-        <v>67</v>
+        <v>84</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" t="s">
-        <v>68</v>
+        <v>85</v>
       </c>
       <c r="B5" t="s">
-        <v>69</v>
+        <v>86</v>
       </c>
       <c r="C5" t="s">
-        <v>70</v>
+        <v>87</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" t="s">
-        <v>71</v>
+        <v>88</v>
       </c>
       <c r="B6" t="s">
-        <v>72</v>
+        <v>89</v>
       </c>
       <c r="C6" t="s">
-        <v>73</v>
+        <v>90</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7" t="s">
-        <v>74</v>
+        <v>91</v>
       </c>
       <c r="B7" t="s">
-        <v>12</v>
+        <v>92</v>
       </c>
       <c r="C7" t="s">
-        <v>75</v>
+        <v>93</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8" t="s">
-        <v>76</v>
+        <v>94</v>
       </c>
       <c r="B8" t="s">
-        <v>77</v>
+        <v>95</v>
       </c>
       <c r="C8" t="s">
-        <v>78</v>
+        <v>96</v>
       </c>
     </row>
     <row r="9" spans="1:3">
       <c r="A9" t="s">
-        <v>79</v>
+        <v>97</v>
       </c>
       <c r="B9" t="s">
-        <v>80</v>
+        <v>98</v>
       </c>
       <c r="C9" t="s">
-        <v>81</v>
+        <v>99</v>
       </c>
     </row>
     <row r="10" spans="1:3">
       <c r="A10" t="s">
-        <v>82</v>
+        <v>100</v>
       </c>
       <c r="B10" t="s">
-        <v>83</v>
+        <v>101</v>
       </c>
       <c r="C10" t="s">
-        <v>84</v>
+        <v>102</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11" t="s">
-        <v>85</v>
+        <v>103</v>
       </c>
       <c r="B11" t="s">
-        <v>86</v>
+        <v>104</v>
       </c>
       <c r="C11" t="s">
-        <v>87</v>
+        <v>105</v>
       </c>
     </row>
     <row r="12" spans="1:3">
       <c r="A12" t="s">
-        <v>88</v>
+        <v>106</v>
       </c>
       <c r="B12" t="s">
-        <v>89</v>
+        <v>107</v>
       </c>
       <c r="C12" t="s">
-        <v>90</v>
+        <v>108</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13" t="s">
-        <v>91</v>
+        <v>109</v>
       </c>
       <c r="B13" t="s">
-        <v>92</v>
+        <v>110</v>
       </c>
       <c r="C13" t="s">
-        <v>93</v>
+        <v>111</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14" t="s">
-        <v>94</v>
+        <v>112</v>
       </c>
       <c r="B14" t="s">
-        <v>95</v>
+        <v>113</v>
       </c>
       <c r="C14" t="s">
-        <v>96</v>
+        <v>114</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15" t="s">
-        <v>97</v>
+        <v>115</v>
       </c>
       <c r="B15" t="s">
-        <v>98</v>
+        <v>116</v>
       </c>
       <c r="C15" t="s">
-        <v>99</v>
+        <v>117</v>
       </c>
     </row>
   </sheetData>
@@ -3249,7 +3449,7 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="B2:J41"/>
+  <dimension ref="B2:J56"/>
   <sheetFormatPr defaultColWidth="9.14285714285714" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="9.14285714285714" style="1"/>
@@ -3267,15 +3467,15 @@
   <sheetData>
     <row r="2" spans="2:10">
       <c r="B2" s="3" t="s">
-        <v>100</v>
+        <v>118</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>101</v>
+        <v>119</v>
       </c>
       <c r="D2" s="3"/>
       <c r="E2" s="3"/>
       <c r="G2" s="3" t="s">
-        <v>102</v>
+        <v>120</v>
       </c>
       <c r="H2" s="4"/>
       <c r="I2" s="3"/>
@@ -3283,19 +3483,19 @@
     </row>
     <row r="3" spans="2:10">
       <c r="B3" s="5" t="s">
-        <v>103</v>
+        <v>121</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>104</v>
+        <v>122</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>105</v>
+        <v>71</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>106</v>
+        <v>123</v>
       </c>
       <c r="G3" s="5" t="s">
-        <v>107</v>
+        <v>124</v>
       </c>
       <c r="H3" s="5"/>
       <c r="I3" s="5"/>
@@ -3306,25 +3506,25 @@
         <v>0</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>108</v>
+        <v>125</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>109</v>
+        <v>126</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>7</v>
+        <v>127</v>
       </c>
       <c r="G4" s="6" t="s">
-        <v>103</v>
+        <v>121</v>
       </c>
       <c r="H4" s="6" t="s">
-        <v>104</v>
+        <v>122</v>
       </c>
       <c r="I4" s="6" t="s">
-        <v>105</v>
+        <v>71</v>
       </c>
       <c r="J4" s="6" t="s">
-        <v>106</v>
+        <v>123</v>
       </c>
     </row>
     <row r="5" spans="2:10">
@@ -3332,10 +3532,10 @@
         <v>1</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>108</v>
+        <v>125</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>110</v>
+        <v>128</v>
       </c>
       <c r="E5" s="6" t="s">
         <v>8</v>
@@ -3344,13 +3544,13 @@
         <v>2</v>
       </c>
       <c r="H5" s="5" t="s">
-        <v>108</v>
+        <v>125</v>
       </c>
       <c r="I5" s="5" t="s">
-        <v>111</v>
+        <v>129</v>
       </c>
       <c r="J5" s="5" t="s">
-        <v>9</v>
+        <v>42</v>
       </c>
     </row>
     <row r="6" spans="2:10">
@@ -3358,22 +3558,22 @@
         <v>2</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>108</v>
+        <v>125</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>112</v>
+        <v>130</v>
       </c>
       <c r="E6" s="5" t="s">
-        <v>9</v>
+        <v>42</v>
       </c>
       <c r="G6" s="6" t="s">
         <v>3</v>
       </c>
       <c r="H6" s="6" t="s">
-        <v>108</v>
+        <v>125</v>
       </c>
       <c r="I6" s="6" t="s">
-        <v>113</v>
+        <v>131</v>
       </c>
       <c r="J6" s="6" t="s">
         <v>10</v>
@@ -3384,22 +3584,22 @@
         <v>3</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>108</v>
+        <v>125</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>114</v>
+        <v>132</v>
       </c>
       <c r="E7" s="6" t="s">
         <v>10</v>
       </c>
       <c r="G7" s="5" t="s">
-        <v>48</v>
+        <v>59</v>
       </c>
       <c r="H7" s="5" t="s">
-        <v>115</v>
+        <v>133</v>
       </c>
       <c r="I7" s="5" t="s">
-        <v>116</v>
+        <v>134</v>
       </c>
       <c r="J7" s="5">
         <v>5</v>
@@ -3410,22 +3610,22 @@
         <v>4</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>108</v>
+        <v>125</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>117</v>
+        <v>135</v>
       </c>
       <c r="E8" s="5" t="s">
-        <v>118</v>
+        <v>136</v>
       </c>
       <c r="G8" s="6" t="s">
-        <v>49</v>
+        <v>60</v>
       </c>
       <c r="H8" s="6" t="s">
-        <v>115</v>
+        <v>133</v>
       </c>
       <c r="I8" s="6" t="s">
-        <v>119</v>
+        <v>137</v>
       </c>
       <c r="J8" s="6">
         <v>5</v>
@@ -3436,22 +3636,22 @@
         <v>5</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>115</v>
+        <v>133</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>120</v>
+        <v>138</v>
       </c>
       <c r="E9" s="6">
         <v>3</v>
       </c>
       <c r="G9" s="5" t="s">
-        <v>50</v>
+        <v>61</v>
       </c>
       <c r="H9" s="5" t="s">
-        <v>115</v>
+        <v>133</v>
       </c>
       <c r="I9" s="5" t="s">
-        <v>121</v>
+        <v>139</v>
       </c>
       <c r="J9" s="5">
         <v>1</v>
@@ -3462,22 +3662,22 @@
         <v>6</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>115</v>
+        <v>133</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>122</v>
+        <v>140</v>
       </c>
       <c r="E10" s="5">
         <v>1</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>51</v>
+        <v>62</v>
       </c>
       <c r="H10" s="4" t="s">
-        <v>115</v>
+        <v>133</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>123</v>
+        <v>141</v>
       </c>
       <c r="J10" s="3">
         <v>1</v>
@@ -3485,13 +3685,13 @@
     </row>
     <row r="11" spans="2:10">
       <c r="G11" s="5" t="s">
-        <v>52</v>
+        <v>63</v>
       </c>
       <c r="H11" s="5" t="s">
-        <v>115</v>
+        <v>133</v>
       </c>
       <c r="I11" s="5" t="s">
-        <v>124</v>
+        <v>142</v>
       </c>
       <c r="J11" s="5">
         <v>3</v>
@@ -3499,23 +3699,23 @@
     </row>
     <row r="12" spans="2:10">
       <c r="B12" s="3" t="s">
-        <v>125</v>
+        <v>143</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>126</v>
+        <v>144</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>127</v>
+        <v>145</v>
       </c>
       <c r="E12" s="3"/>
       <c r="G12" s="5" t="s">
-        <v>53</v>
+        <v>64</v>
       </c>
       <c r="H12" s="5" t="s">
-        <v>115</v>
+        <v>133</v>
       </c>
       <c r="I12" s="5" t="s">
-        <v>128</v>
+        <v>146</v>
       </c>
       <c r="J12" s="5">
         <v>0</v>
@@ -3523,16 +3723,16 @@
     </row>
     <row r="13" spans="2:10">
       <c r="B13" s="5" t="s">
-        <v>103</v>
+        <v>121</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>104</v>
+        <v>122</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>105</v>
+        <v>71</v>
       </c>
       <c r="E13" s="5" t="s">
-        <v>106</v>
+        <v>123</v>
       </c>
     </row>
     <row r="14" spans="2:10">
@@ -3540,174 +3740,174 @@
         <v>1</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>108</v>
+        <v>125</v>
       </c>
       <c r="D14" s="5" t="s">
-        <v>129</v>
+        <v>147</v>
       </c>
       <c r="E14" s="5" t="s">
         <v>8</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>130</v>
+        <v>148</v>
       </c>
       <c r="H14" s="4"/>
       <c r="I14" s="3"/>
     </row>
     <row r="15" spans="2:10">
       <c r="B15" s="6" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C15" s="6" t="s">
-        <v>108</v>
+        <v>125</v>
       </c>
       <c r="D15" s="6" t="s">
-        <v>131</v>
+        <v>149</v>
       </c>
       <c r="E15" s="6" t="s">
         <v>8</v>
       </c>
       <c r="G15" s="5" t="s">
-        <v>132</v>
+        <v>150</v>
       </c>
       <c r="H15" s="5"/>
       <c r="I15" s="5"/>
     </row>
     <row r="16" ht="15" spans="2:10">
       <c r="B16" s="5" t="s">
+        <v>151</v>
+      </c>
+      <c r="C16" s="5" t="s">
         <v>133</v>
       </c>
-      <c r="C16" s="5" t="s">
-        <v>115</v>
-      </c>
       <c r="D16" s="5" t="s">
-        <v>134</v>
+        <v>152</v>
       </c>
       <c r="E16" s="5" t="s">
-        <v>135</v>
+        <v>153</v>
       </c>
       <c r="G16" s="5" t="s">
-        <v>56</v>
+        <v>73</v>
       </c>
       <c r="H16" s="5" t="s">
-        <v>136</v>
+        <v>154</v>
       </c>
       <c r="I16" s="5" t="s">
-        <v>105</v>
+        <v>71</v>
       </c>
     </row>
     <row r="17" ht="15" spans="2:9">
       <c r="B17" s="6" t="s">
-        <v>137</v>
+        <v>155</v>
       </c>
       <c r="C17" s="6" t="s">
-        <v>115</v>
+        <v>133</v>
       </c>
       <c r="D17" s="6" t="s">
-        <v>138</v>
+        <v>156</v>
       </c>
       <c r="E17" s="6" t="s">
-        <v>135</v>
+        <v>153</v>
       </c>
       <c r="G17" s="6" t="s">
-        <v>59</v>
+        <v>76</v>
       </c>
       <c r="H17" s="6">
         <v>42</v>
       </c>
       <c r="I17" s="6" t="s">
-        <v>61</v>
+        <v>78</v>
       </c>
     </row>
     <row r="18" ht="15" spans="2:9">
       <c r="B18" s="5" t="s">
-        <v>139</v>
+        <v>157</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>115</v>
+        <v>133</v>
       </c>
       <c r="D18" s="5" t="s">
-        <v>140</v>
+        <v>158</v>
       </c>
       <c r="E18" s="5" t="s">
-        <v>141</v>
+        <v>159</v>
       </c>
       <c r="G18" s="5" t="s">
-        <v>62</v>
+        <v>79</v>
       </c>
       <c r="H18" s="5" t="s">
-        <v>63</v>
+        <v>80</v>
       </c>
       <c r="I18" s="5" t="s">
-        <v>64</v>
+        <v>81</v>
       </c>
     </row>
     <row r="19" spans="2:9">
       <c r="G19" s="6" t="s">
-        <v>65</v>
+        <v>82</v>
       </c>
       <c r="H19" s="6" t="s">
-        <v>66</v>
+        <v>83</v>
       </c>
       <c r="I19" s="6" t="s">
-        <v>142</v>
+        <v>160</v>
       </c>
     </row>
     <row r="20" spans="2:9">
       <c r="B20" s="3" t="s">
-        <v>143</v>
+        <v>161</v>
       </c>
       <c r="C20" s="3"/>
       <c r="D20" s="3"/>
       <c r="E20" s="3"/>
       <c r="G20" s="5" t="s">
-        <v>68</v>
+        <v>85</v>
       </c>
       <c r="H20" s="5" t="s">
-        <v>69</v>
+        <v>86</v>
       </c>
       <c r="I20" s="5" t="s">
-        <v>144</v>
+        <v>162</v>
       </c>
     </row>
     <row r="21" ht="15" spans="2:9">
       <c r="B21" s="5" t="s">
-        <v>145</v>
+        <v>163</v>
       </c>
       <c r="C21" s="5"/>
       <c r="D21" s="5"/>
       <c r="E21" s="5"/>
       <c r="G21" s="6" t="s">
-        <v>71</v>
+        <v>88</v>
       </c>
       <c r="H21" s="6" t="s">
-        <v>72</v>
+        <v>89</v>
       </c>
       <c r="I21" s="6" t="s">
-        <v>146</v>
+        <v>164</v>
       </c>
     </row>
     <row r="22" spans="2:9">
       <c r="B22" s="6" t="s">
-        <v>103</v>
+        <v>121</v>
       </c>
       <c r="C22" s="6" t="s">
-        <v>104</v>
+        <v>122</v>
       </c>
       <c r="D22" s="6" t="s">
-        <v>105</v>
+        <v>71</v>
       </c>
       <c r="E22" s="6" t="s">
-        <v>106</v>
+        <v>123</v>
       </c>
       <c r="G22" s="5" t="s">
-        <v>74</v>
+        <v>91</v>
       </c>
       <c r="H22" s="5">
         <v>1</v>
       </c>
       <c r="I22" s="5" t="s">
-        <v>147</v>
+        <v>165</v>
       </c>
     </row>
     <row r="23" spans="2:9">
@@ -3715,310 +3915,563 @@
         <v>1</v>
       </c>
       <c r="C23" s="5" t="s">
-        <v>108</v>
+        <v>125</v>
       </c>
       <c r="D23" s="5" t="s">
-        <v>148</v>
+        <v>166</v>
       </c>
       <c r="E23" s="5" t="s">
         <v>8</v>
       </c>
       <c r="G23" s="3" t="s">
-        <v>76</v>
+        <v>94</v>
       </c>
       <c r="H23" s="4">
         <v>0</v>
       </c>
       <c r="I23" s="3" t="s">
-        <v>149</v>
+        <v>167</v>
       </c>
     </row>
     <row r="24" spans="2:9">
       <c r="B24" s="6" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C24" s="6" t="s">
-        <v>115</v>
+        <v>133</v>
       </c>
       <c r="D24" s="6" t="s">
-        <v>150</v>
+        <v>168</v>
       </c>
       <c r="E24" s="6">
         <v>100</v>
       </c>
       <c r="G24" s="5" t="s">
-        <v>79</v>
+        <v>97</v>
       </c>
       <c r="H24" s="5" t="s">
-        <v>80</v>
+        <v>98</v>
       </c>
       <c r="I24" s="5" t="s">
-        <v>151</v>
+        <v>169</v>
       </c>
     </row>
     <row r="25" spans="2:9">
       <c r="B25" s="5" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C25" s="5" t="s">
-        <v>115</v>
+        <v>133</v>
       </c>
       <c r="D25" s="5" t="s">
-        <v>152</v>
+        <v>170</v>
       </c>
       <c r="E25" s="5">
         <v>5</v>
       </c>
       <c r="G25" s="5" t="s">
-        <v>82</v>
+        <v>100</v>
       </c>
       <c r="H25" s="5">
         <v>800</v>
       </c>
       <c r="I25" s="5" t="s">
-        <v>84</v>
+        <v>102</v>
       </c>
     </row>
     <row r="26" spans="2:9">
       <c r="B26" s="3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>115</v>
+        <v>133</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>153</v>
+        <v>171</v>
       </c>
       <c r="E26" s="4">
         <v>8</v>
       </c>
       <c r="G26" s="6" t="s">
-        <v>85</v>
+        <v>103</v>
       </c>
       <c r="H26" s="6">
         <v>600</v>
       </c>
       <c r="I26" s="6" t="s">
-        <v>87</v>
+        <v>105</v>
       </c>
     </row>
     <row r="27" spans="2:9">
       <c r="B27" s="5" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C27" s="5" t="s">
-        <v>115</v>
+        <v>133</v>
       </c>
       <c r="D27" s="5" t="s">
-        <v>154</v>
+        <v>172</v>
       </c>
       <c r="E27" s="5">
         <v>3</v>
       </c>
       <c r="G27" s="5" t="s">
-        <v>88</v>
+        <v>106</v>
       </c>
       <c r="H27" s="5">
         <v>1.8</v>
       </c>
       <c r="I27" s="5" t="s">
-        <v>90</v>
+        <v>108</v>
       </c>
     </row>
     <row r="28" ht="15" spans="2:9">
       <c r="B28" s="5" t="s">
-        <v>155</v>
+        <v>173</v>
       </c>
       <c r="C28" s="5" t="s">
-        <v>115</v>
+        <v>133</v>
       </c>
       <c r="D28" s="5" t="s">
-        <v>156</v>
+        <v>174</v>
       </c>
       <c r="E28" s="5">
         <v>46236</v>
       </c>
       <c r="G28" s="6" t="s">
-        <v>91</v>
+        <v>109</v>
       </c>
       <c r="H28" s="6">
         <v>12</v>
       </c>
       <c r="I28" s="6" t="s">
-        <v>93</v>
+        <v>111</v>
       </c>
     </row>
     <row r="29" ht="15" spans="2:9">
       <c r="B29" s="6" t="s">
-        <v>157</v>
+        <v>175</v>
       </c>
       <c r="C29" s="6" t="s">
-        <v>115</v>
+        <v>133</v>
       </c>
       <c r="D29" s="6" t="s">
-        <v>158</v>
+        <v>176</v>
       </c>
       <c r="E29" s="6">
         <v>46113</v>
       </c>
       <c r="G29" s="5" t="s">
-        <v>94</v>
+        <v>112</v>
       </c>
       <c r="H29" s="5" t="s">
-        <v>95</v>
+        <v>113</v>
       </c>
       <c r="I29" s="5" t="s">
-        <v>159</v>
+        <v>177</v>
       </c>
     </row>
     <row r="30" ht="15" spans="2:9">
       <c r="B30" s="5" t="s">
-        <v>160</v>
+        <v>178</v>
       </c>
       <c r="C30" s="5" t="s">
+        <v>133</v>
+      </c>
+      <c r="D30" s="5" t="s">
+        <v>179</v>
+      </c>
+      <c r="E30" s="5" t="s">
+        <v>180</v>
+      </c>
+      <c r="G30" s="6" t="s">
         <v>115</v>
       </c>
-      <c r="D30" s="5" t="s">
-        <v>161</v>
-      </c>
-      <c r="E30" s="5" t="s">
-        <v>162</v>
-      </c>
-      <c r="G30" s="6" t="s">
-        <v>97</v>
-      </c>
       <c r="H30" s="6" t="s">
-        <v>98</v>
+        <v>116</v>
       </c>
       <c r="I30" s="6" t="s">
-        <v>163</v>
+        <v>181</v>
       </c>
     </row>
     <row r="32" spans="2:9">
       <c r="B32" s="3" t="s">
-        <v>164</v>
+        <v>182</v>
       </c>
       <c r="C32" s="3"/>
       <c r="D32" s="3"/>
       <c r="E32" s="3"/>
     </row>
-    <row r="33" spans="2:5">
+    <row r="33" spans="2:8">
       <c r="B33" s="5" t="s">
-        <v>165</v>
+        <v>183</v>
       </c>
       <c r="C33" s="5"/>
       <c r="D33" s="5"/>
       <c r="E33" s="5"/>
     </row>
-    <row r="34" spans="2:5">
+    <row r="34" spans="2:8">
       <c r="B34" s="6" t="s">
-        <v>103</v>
+        <v>121</v>
       </c>
       <c r="C34" s="6" t="s">
-        <v>104</v>
+        <v>122</v>
       </c>
       <c r="D34" s="6" t="s">
-        <v>105</v>
+        <v>71</v>
       </c>
       <c r="E34" s="6" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="35" spans="2:5">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="35" spans="2:8">
       <c r="B35" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C35" s="5" t="s">
-        <v>108</v>
+        <v>125</v>
       </c>
       <c r="D35" s="5" t="s">
-        <v>166</v>
+        <v>184</v>
       </c>
       <c r="E35" s="5" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="36" spans="2:8">
+      <c r="B36" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="C36" s="6" t="s">
+        <v>125</v>
+      </c>
+      <c r="D36" s="6" t="s">
+        <v>185</v>
+      </c>
+      <c r="E36" s="6" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="37" spans="2:8">
+      <c r="B37" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="C37" s="5" t="s">
+        <v>125</v>
+      </c>
+      <c r="D37" s="5" t="s">
+        <v>186</v>
+      </c>
+      <c r="E37" s="5" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="38" ht="15" spans="2:8">
+      <c r="B38" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="C38" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="D38" s="3" t="s">
+        <v>187</v>
+      </c>
+      <c r="E38" s="3" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="39" spans="2:8">
+      <c r="B39" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="C39" s="5" t="s">
+        <v>125</v>
+      </c>
+      <c r="D39" s="5" t="s">
+        <v>189</v>
+      </c>
+      <c r="E39" s="5" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="40" spans="2:8">
+      <c r="B40" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="C40" s="5" t="s">
+        <v>125</v>
+      </c>
+      <c r="D40" s="5" t="s">
+        <v>190</v>
+      </c>
+      <c r="E40" s="5" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="41" spans="2:8">
+      <c r="B41" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="C41" s="6" t="s">
+        <v>133</v>
+      </c>
+      <c r="D41" s="6" t="s">
+        <v>191</v>
+      </c>
+      <c r="E41" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="46" ht="15" spans="2:8">
+      <c r="B46" s="7" t="s">
+        <v>127</v>
+      </c>
+      <c r="C46" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="D46" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="E46" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="F46" s="7">
+        <v>2</v>
+      </c>
+      <c r="G46" s="7">
+        <v>1</v>
+      </c>
+      <c r="H46" s="7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="47" ht="15" spans="2:8">
+      <c r="B47" s="7" t="s">
+        <v>127</v>
+      </c>
+      <c r="C47" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="D47" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="E47" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="F47" s="7">
+        <v>3</v>
+      </c>
+      <c r="G47" s="7">
+        <v>1</v>
+      </c>
+      <c r="H47" s="7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="48" ht="15" spans="2:8">
+      <c r="B48" s="7" t="s">
+        <v>127</v>
+      </c>
+      <c r="C48" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="D48" s="7" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="36" spans="2:5">
-      <c r="B36" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="C36" s="6" t="s">
-        <v>108</v>
-      </c>
-      <c r="D36" s="6" t="s">
-        <v>167</v>
-      </c>
-      <c r="E36" s="6" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="37" spans="2:5">
-      <c r="B37" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="C37" s="5" t="s">
-        <v>108</v>
-      </c>
-      <c r="D37" s="5" t="s">
-        <v>168</v>
-      </c>
-      <c r="E37" s="5" t="s">
+      <c r="E48" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="F48" s="7" t="s">
+        <v>92</v>
+      </c>
+      <c r="G48" s="7">
+        <v>1</v>
+      </c>
+      <c r="H48" s="7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="49" ht="15" spans="2:8">
+      <c r="B49" s="7" t="s">
+        <v>127</v>
+      </c>
+      <c r="C49" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="D49" s="7" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="38" ht="15" spans="2:5">
-      <c r="B38" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="C38" s="3" t="s">
-        <v>108</v>
-      </c>
-      <c r="D38" s="3" t="s">
-        <v>169</v>
-      </c>
-      <c r="E38" s="3" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="39" spans="2:5">
-      <c r="B39" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="C39" s="5" t="s">
-        <v>108</v>
-      </c>
-      <c r="D39" s="5" t="s">
-        <v>171</v>
-      </c>
-      <c r="E39" s="5" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="40" spans="2:5">
-      <c r="B40" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="C40" s="5" t="s">
-        <v>108</v>
-      </c>
-      <c r="D40" s="5" t="s">
-        <v>172</v>
-      </c>
-      <c r="E40" s="5" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="41" spans="2:5">
-      <c r="B41" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="C41" s="6" t="s">
-        <v>115</v>
-      </c>
-      <c r="D41" s="6" t="s">
-        <v>173</v>
-      </c>
-      <c r="E41" s="6">
+      <c r="E49" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="F49" s="7">
+        <v>2</v>
+      </c>
+      <c r="G49" s="7">
+        <v>1</v>
+      </c>
+      <c r="H49" s="7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="50" ht="15" spans="2:8">
+      <c r="B50" s="7" t="s">
+        <v>127</v>
+      </c>
+      <c r="C50" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="D50" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="E50" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="F50" s="7">
+        <v>3</v>
+      </c>
+      <c r="G50" s="7">
+        <v>1</v>
+      </c>
+      <c r="H50" s="7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="51" ht="15" spans="2:8">
+      <c r="B51" s="7" t="s">
+        <v>127</v>
+      </c>
+      <c r="C51" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="D51" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="E51" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="F51" s="7" t="s">
+        <v>92</v>
+      </c>
+      <c r="G51" s="7">
+        <v>1</v>
+      </c>
+      <c r="H51" s="7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="52" ht="15" spans="2:8">
+      <c r="B52" s="7" t="s">
+        <v>127</v>
+      </c>
+      <c r="C52" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="D52" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="E52" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="F52" s="7">
+        <v>2</v>
+      </c>
+      <c r="G52" s="7">
+        <v>1</v>
+      </c>
+      <c r="H52" s="7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="53" ht="15" spans="2:8">
+      <c r="B53" s="7" t="s">
+        <v>127</v>
+      </c>
+      <c r="C53" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="D53" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="E53" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="F53" s="7">
+        <v>3</v>
+      </c>
+      <c r="G53" s="7">
+        <v>1</v>
+      </c>
+      <c r="H53" s="7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="54" ht="15" spans="2:8">
+      <c r="B54" s="7" t="s">
+        <v>127</v>
+      </c>
+      <c r="C54" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="D54" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="E54" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="F54" s="7" t="s">
+        <v>92</v>
+      </c>
+      <c r="G54" s="7">
+        <v>1</v>
+      </c>
+      <c r="H54" s="7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="55" ht="15" spans="2:8">
+      <c r="B55" s="7" t="s">
+        <v>127</v>
+      </c>
+      <c r="C55" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="D55" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="E55" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="F55" s="7">
+        <v>2</v>
+      </c>
+      <c r="G55" s="7">
+        <v>1</v>
+      </c>
+      <c r="H55" s="7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="56" ht="15" spans="2:8">
+      <c r="B56" s="7" t="s">
+        <v>127</v>
+      </c>
+      <c r="C56" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="D56" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="E56" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="F56" s="7">
+        <v>3</v>
+      </c>
+      <c r="G56" s="7">
+        <v>1</v>
+      </c>
+      <c r="H56" s="7">
         <v>1</v>
       </c>
     </row>

--- a/a.输入/批量实验配置.xlsx
+++ b/a.输入/批量实验配置.xlsx
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="433" uniqueCount="192">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="449" uniqueCount="192">
   <si>
     <t>group_id</t>
   </si>
@@ -1165,15 +1165,15 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="10.8"/>
+      <color rgb="FF333333"/>
+      <name val="var(--monospace)"/>
+      <charset val="134"/>
+    </font>
+    <font>
       <sz val="12"/>
       <color rgb="FF333333"/>
       <name val="Helvetica"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="10.8"/>
-      <color rgb="FF333333"/>
-      <name val="var(--monospace)"/>
       <charset val="134"/>
     </font>
     <font>
@@ -2221,8 +2221,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:I7"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" outlineLevelRow="6"/>
+  <dimension ref="A1:I10"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="2" width="16.2857142857143" customWidth="1"/>
     <col min="3" max="3" width="36.7142857142857" customWidth="1"/>
@@ -2287,13 +2287,13 @@
         <v>8</v>
       </c>
       <c r="C3" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D3" t="s">
         <v>10</v>
       </c>
       <c r="E3" s="7">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F3" s="7">
         <v>1</v>
@@ -2311,7 +2311,7 @@
         <v>8</v>
       </c>
       <c r="C4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D4" t="s">
         <v>10</v>
@@ -2335,29 +2335,127 @@
         <v>8</v>
       </c>
       <c r="C5" t="s">
+        <v>11</v>
+      </c>
+      <c r="D5" t="s">
+        <v>10</v>
+      </c>
+      <c r="E5" s="7">
+        <v>2</v>
+      </c>
+      <c r="F5" s="7">
+        <v>1</v>
+      </c>
+      <c r="G5" s="7">
+        <v>1</v>
+      </c>
+      <c r="I5" s="11"/>
+    </row>
+    <row r="6" spans="1:9">
+      <c r="A6" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="B6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C6" t="s">
+        <v>12</v>
+      </c>
+      <c r="D6" t="s">
+        <v>10</v>
+      </c>
+      <c r="E6" s="7">
+        <v>1</v>
+      </c>
+      <c r="F6" s="7">
+        <v>1</v>
+      </c>
+      <c r="G6" s="7">
+        <v>1</v>
+      </c>
+      <c r="I6" s="11"/>
+    </row>
+    <row r="7" spans="1:9">
+      <c r="A7" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="B7" t="s">
+        <v>8</v>
+      </c>
+      <c r="C7" t="s">
+        <v>12</v>
+      </c>
+      <c r="D7" t="s">
+        <v>10</v>
+      </c>
+      <c r="E7" s="7">
+        <v>2</v>
+      </c>
+      <c r="F7" s="7">
+        <v>1</v>
+      </c>
+      <c r="G7" s="7">
+        <v>1</v>
+      </c>
+      <c r="I7" s="11"/>
+    </row>
+    <row r="8" spans="1:9">
+      <c r="A8" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="B8" t="s">
+        <v>8</v>
+      </c>
+      <c r="C8" t="s">
         <v>13</v>
       </c>
-      <c r="D5" s="7" t="s">
+      <c r="D8" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="E5" s="7">
-        <v>1</v>
-      </c>
-      <c r="F5" s="7">
-        <v>1</v>
-      </c>
-      <c r="G5" s="7">
-        <v>1</v>
-      </c>
-      <c r="I5" s="11"/>
-    </row>
-    <row r="7" spans="1:9">
-      <c r="A7" s="7"/>
-      <c r="B7" s="7"/>
-      <c r="D7" s="7"/>
-      <c r="E7" s="7"/>
-      <c r="F7" s="7"/>
-      <c r="G7" s="7"/>
+      <c r="E8" s="7">
+        <v>1</v>
+      </c>
+      <c r="F8" s="7">
+        <v>1</v>
+      </c>
+      <c r="G8" s="7">
+        <v>1</v>
+      </c>
+      <c r="I8" s="11"/>
+    </row>
+    <row r="9" spans="1:9">
+      <c r="A9" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="B9" t="s">
+        <v>8</v>
+      </c>
+      <c r="C9" t="s">
+        <v>13</v>
+      </c>
+      <c r="D9" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="E9" s="7">
+        <v>2</v>
+      </c>
+      <c r="F9" s="7">
+        <v>1</v>
+      </c>
+      <c r="G9" s="7">
+        <v>1</v>
+      </c>
+      <c r="I9" s="11"/>
+    </row>
+    <row r="10" spans="1:9">
+      <c r="A10" s="7"/>
+      <c r="B10"/>
+      <c r="C10"/>
+      <c r="D10" s="7"/>
+      <c r="E10" s="7"/>
+      <c r="F10" s="7"/>
+      <c r="G10" s="7"/>
+      <c r="I10" s="11"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/a.输入/批量实验配置.xlsx
+++ b/a.输入/批量实验配置.xlsx
@@ -2719,7 +2719,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J25"/>
+  <dimension ref="A1:J26"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
     <col width="33.1428571428571" customWidth="1" min="1" max="1"/>
@@ -2892,6 +2892,7 @@
         <v>1</v>
       </c>
     </row>
+    <row r="5"/>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
@@ -2964,6 +2965,14 @@
         <v>1</v>
       </c>
     </row>
+    <row r="8"/>
+    <row r="9"/>
+    <row r="10"/>
+    <row r="11"/>
+    <row r="12"/>
+    <row r="13"/>
+    <row r="14"/>
+    <row r="15"/>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
@@ -3322,6 +3331,42 @@
       </c>
       <c r="J25" t="n">
         <v>0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>RDA</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Without share weighting</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>5</v>
+      </c>
+      <c r="D26" t="n">
+        <v>5</v>
+      </c>
+      <c r="E26" t="n">
+        <v>0</v>
+      </c>
+      <c r="F26" t="n">
+        <v>1</v>
+      </c>
+      <c r="G26" t="n">
+        <v>2</v>
+      </c>
+      <c r="H26" t="n">
+        <v>0</v>
+      </c>
+      <c r="I26" t="n">
+        <v>1</v>
+      </c>
+      <c r="J26" t="n">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
